--- a/demo_data/sectors/uretim_sanayi/mizan_prior.xlsx
+++ b/demo_data/sectors/uretim_sanayi/mizan_prior.xlsx
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3654612.39</v>
+        <v>3654612.4</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>329047.11</v>
+        <v>329047.12</v>
       </c>
     </row>
     <row r="45">
